--- a/docs/validation/V17_Report_to_Model_Binding.xlsx
+++ b/docs/validation/V17_Report_to_Model_Binding.xlsx
@@ -1183,13 +1183,13 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="16" customHeight="1">
+    <row r="48" ht="29.5" customHeight="1">
       <c r="A48" s="16" t="n">
         <v>5</v>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Also check the .Report folder holds no SemanticModel folder and no .tmdl files — a thin report has no model definition of its own.</t>
+          <t>Also check that no folder with the report’s name and .SemanticModel on the end (for example R1_Retail_Sector_Health.SemanticModel) sits beside the .Report folder, and that the .Report folder holds no .tmdl files — a thin report has no model definition of its own.</t>
         </is>
       </c>
     </row>

--- a/docs/validation/V17_Report_to_Model_Binding.xlsx
+++ b/docs/validation/V17_Report_to_Model_Binding.xlsx
@@ -2062,7 +2062,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F50:F52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A"</formula1>
+      <formula1>"Pass,Fail,N/A,Not run"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
